--- a/results_(stress_test)_summary/competitors_f(AEC,PS)/cnn_evaluation(stress_test)_type-multiplicative_nm_basis-False_nm_modifier-False.xlsx
+++ b/results_(stress_test)_summary/competitors_f(AEC,PS)/cnn_evaluation(stress_test)_type-multiplicative_nm_basis-False_nm_modifier-False.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_cnn_subnetwork_evaluation\competitors_f(AEC,PS)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_summary\competitors_f(AEC,PS)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787DFC12-4E27-4858-801C-F75E3E3D0222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CF4F12D-E5D3-44FB-AAB1-1DC84D950971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -151,19 +151,19 @@
     <t>Std</t>
   </si>
   <si>
-    <t>PCCxSigmoid(PLV)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PCCxSigmoid(PLI)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>std</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>f1 score</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PCC,PLV</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PCC,PLI</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -250,7 +250,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -570,7 +570,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
@@ -1134,7 +1134,7 @@
         <v>4</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.15">
@@ -1694,10 +1694,10 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.15">
@@ -2182,10 +2182,10 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.15">
@@ -2193,25 +2193,25 @@
         <v>1</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.15">
@@ -2448,7 +2448,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B29">
         <v>3.945711842949601</v>
@@ -2472,7 +2472,7 @@
         <v>8.7433484877826491</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K29">
         <v>3.190312271555559</v>
@@ -2498,7 +2498,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B30">
         <v>92.778947400409621</v>
@@ -2522,7 +2522,7 @@
         <v>48.584106437626268</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K30">
         <v>91.377634404932721</v>
@@ -2548,7 +2548,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B31">
         <v>4.3743918396131134</v>
@@ -2572,7 +2572,7 @@
         <v>9.2918474149187738</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K31">
         <v>3.5684194304484111</v>
@@ -2624,7 +2624,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
@@ -3188,7 +3188,7 @@
         <v>4</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.15">
@@ -3763,7 +3763,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
@@ -4327,7 +4327,7 @@
         <v>4</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.15">
@@ -4902,7 +4902,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
@@ -5466,7 +5466,7 @@
         <v>4</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.15">
@@ -6041,7 +6041,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
@@ -6605,7 +6605,7 @@
         <v>4</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.15">
@@ -7180,7 +7180,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
@@ -7744,7 +7744,7 @@
         <v>4</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.15">
@@ -8319,7 +8319,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
@@ -8883,7 +8883,7 @@
         <v>4</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.15">
